--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB15E7-87C4-48C2-86FE-0E13B8012BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9AE5E4-23D9-431F-B346-5BD41A999FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -513,6 +513,14 @@
   </si>
   <si>
     <t>김경집</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김영택</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1544,6 +1552,30 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1556,21 +1588,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,15 +1604,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1963,52 +1971,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2048,12 +2056,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2061,7 +2069,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2073,7 +2081,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2238,10 +2246,18 @@
       <c r="O10" s="32">
         <v>5</v>
       </c>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="30"/>
+      <c r="Q10" s="23">
+        <v>46303</v>
+      </c>
+      <c r="R10" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="S10" s="28">
+        <v>50</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="Y10"/>
       <c r="AD10"/>
     </row>
@@ -2249,7 +2265,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2286,7 +2302,7 @@
       </c>
       <c r="S11" s="29">
         <f>SUM(S7:S10)</f>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="T11" s="11"/>
       <c r="Y11"/>
@@ -2296,7 +2312,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2332,7 +2348,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2342,7 +2358,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2363,10 +2379,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2380,7 +2396,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2390,7 +2406,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2409,13 +2425,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="69" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2425,7 +2441,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2435,7 +2451,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2454,13 +2470,13 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="T15" s="16"/>
       <c r="Y15"/>
@@ -2470,7 +2486,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2480,7 +2496,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2501,13 +2517,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1577</v>
+        <v>1632</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2519,7 +2535,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2531,7 +2547,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2557,7 +2573,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2567,7 +2583,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2594,7 +2610,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2604,7 +2620,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2635,7 +2651,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2645,7 +2661,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2671,7 +2687,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2681,7 +2697,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2707,7 +2723,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2747,7 +2763,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2786,7 +2802,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2824,7 +2840,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2862,7 +2878,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2872,7 +2888,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2884,7 +2900,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="63">
+      <c r="M26" s="57">
         <v>46235</v>
       </c>
       <c r="N26" s="34" t="s">
@@ -2900,7 +2916,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2910,7 +2926,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2920,7 +2936,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="65"/>
+      <c r="M27" s="59"/>
       <c r="N27" s="34" t="s">
         <v>115</v>
       </c>
@@ -2958,9 +2974,15 @@
       <c r="L28" s="3">
         <v>96</v>
       </c>
-      <c r="M28" s="53"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="36"/>
+      <c r="M28" s="53">
+        <v>46272</v>
+      </c>
+      <c r="N28" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="O28" s="36">
+        <v>5</v>
+      </c>
       <c r="Y28"/>
       <c r="AD28"/>
     </row>
@@ -2968,7 +2990,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3108,7 +3130,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3191,7 +3213,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3396,7 +3418,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3491,7 +3513,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3501,15 +3523,6 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3522,6 +3535,15 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9AE5E4-23D9-431F-B346-5BD41A999FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D30F58E-2CE9-4904-8545-A278D5D60927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -516,11 +516,11 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>김영택</t>
+    <t>이영준</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>이영준</t>
+    <t>임국남</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1552,30 +1552,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1588,6 +1564,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1604,6 +1595,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1971,52 +1971,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2056,12 +2056,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2069,7 +2069,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2081,7 +2081,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2250,7 +2250,7 @@
         <v>46303</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S10" s="28">
         <v>50</v>
@@ -2265,7 +2265,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2312,7 +2312,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2348,7 +2348,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2379,10 +2379,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="68"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2396,7 +2396,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2406,7 +2406,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2425,10 +2425,10 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="70"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
         <v>482</v>
@@ -2441,7 +2441,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2451,7 +2451,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2470,10 +2470,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="70"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1150</v>
@@ -2486,7 +2486,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2517,10 +2517,10 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="63" t="s">
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="64"/>
+      <c r="R16" s="74"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
         <v>1632</v>
@@ -2535,7 +2535,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2547,7 +2547,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2573,7 +2573,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2583,7 +2583,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2610,7 +2610,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2620,7 +2620,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2651,7 +2651,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2661,7 +2661,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2687,7 +2687,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="59"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2723,7 +2723,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2763,7 +2763,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="58"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2802,7 +2802,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2840,7 +2840,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2900,7 +2900,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="57">
+      <c r="M26" s="63">
         <v>46235</v>
       </c>
       <c r="N26" s="34" t="s">
@@ -2916,7 +2916,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2926,7 +2926,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="58"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="59"/>
+      <c r="M27" s="65"/>
       <c r="N27" s="34" t="s">
         <v>115</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>46272</v>
       </c>
       <c r="N28" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O28" s="36">
         <v>5</v>
@@ -2990,7 +2990,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3130,7 +3130,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3213,7 +3213,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3418,7 +3418,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3523,6 +3523,15 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3535,15 +3544,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D30F58E-2CE9-4904-8545-A278D5D60927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3796E446-0A8C-4C62-9BE6-590396F73EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="121">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -521,6 +521,18 @@
   </si>
   <si>
     <t>임국남</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김주동</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>문만종</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>육광열</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1552,6 +1564,30 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1564,21 +1600,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1595,15 +1616,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1971,52 +1983,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2056,12 +2068,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2069,7 +2081,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2081,7 +2093,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2265,7 +2277,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2312,7 +2324,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2348,7 +2360,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2358,7 +2370,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2379,10 +2391,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2396,7 +2408,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2406,7 +2418,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2425,13 +2437,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="69" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2441,7 +2453,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2451,7 +2463,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2470,10 +2482,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1150</v>
@@ -2486,7 +2498,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2496,7 +2508,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2517,13 +2529,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1632</v>
+        <v>1647</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2535,7 +2547,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2547,7 +2559,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2573,7 +2585,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2583,7 +2595,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2610,7 +2622,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2620,7 +2632,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2651,7 +2663,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2661,7 +2673,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2687,7 +2699,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2697,7 +2709,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2723,7 +2735,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2763,7 +2775,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2802,7 +2814,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2840,7 +2852,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2878,7 +2890,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2888,7 +2900,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2900,7 +2912,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="63">
+      <c r="M26" s="57">
         <v>46235</v>
       </c>
       <c r="N26" s="34" t="s">
@@ -2916,7 +2928,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2926,7 +2938,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2936,7 +2948,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="65"/>
+      <c r="M27" s="59"/>
       <c r="N27" s="34" t="s">
         <v>115</v>
       </c>
@@ -2990,7 +3002,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3014,9 +3026,15 @@
       <c r="L29" s="3">
         <v>97</v>
       </c>
-      <c r="M29" s="53"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="36"/>
+      <c r="M29" s="53">
+        <v>46310</v>
+      </c>
+      <c r="N29" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="O29" s="36">
+        <v>5</v>
+      </c>
       <c r="Y29"/>
       <c r="AD29"/>
     </row>
@@ -3046,9 +3064,15 @@
       <c r="L30" s="3">
         <v>98</v>
       </c>
-      <c r="M30" s="53"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="36"/>
+      <c r="M30" s="53">
+        <v>46311</v>
+      </c>
+      <c r="N30" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="O30" s="36">
+        <v>5</v>
+      </c>
       <c r="Y30"/>
       <c r="AD30"/>
     </row>
@@ -3078,9 +3102,15 @@
       <c r="L31" s="3">
         <v>99</v>
       </c>
-      <c r="M31" s="53"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="36"/>
+      <c r="M31" s="53">
+        <v>46317</v>
+      </c>
+      <c r="N31" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="O31" s="36">
+        <v>5</v>
+      </c>
       <c r="Y31"/>
       <c r="AD31"/>
     </row>
@@ -3130,7 +3160,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3213,7 +3243,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3418,7 +3448,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3513,7 +3543,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3523,15 +3553,6 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3544,6 +3565,15 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3796E446-0A8C-4C62-9BE6-590396F73EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A327D56-5B23-487D-BE83-BFF0D6C43307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -533,6 +533,10 @@
   </si>
   <si>
     <t>육광열</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김창균</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1564,30 +1568,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1600,6 +1580,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1616,6 +1611,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1983,52 +1987,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2068,12 +2072,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2081,7 +2085,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2093,7 +2097,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2277,7 +2281,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2324,7 +2328,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2360,7 +2364,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2370,7 +2374,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2391,10 +2395,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="68"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2408,7 +2412,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2418,7 +2422,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2437,13 +2441,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="70"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2453,7 +2457,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2463,7 +2467,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2482,10 +2486,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="70"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1150</v>
@@ -2498,7 +2502,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2508,7 +2512,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2529,13 +2533,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="63" t="s">
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="64"/>
+      <c r="R16" s="74"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2547,7 +2551,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2559,7 +2563,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2585,7 +2589,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2599,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2622,7 +2626,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2632,7 +2636,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2663,7 +2667,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2673,7 +2677,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2699,7 +2703,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2709,7 +2713,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="59"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2735,7 +2739,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2775,7 +2779,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="58"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2814,7 +2818,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2852,7 +2856,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2890,7 +2894,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2900,7 +2904,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2912,7 +2916,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="57">
+      <c r="M26" s="63">
         <v>46235</v>
       </c>
       <c r="N26" s="34" t="s">
@@ -2928,7 +2932,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2938,7 +2942,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="58"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2948,7 +2952,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="59"/>
+      <c r="M27" s="65"/>
       <c r="N27" s="34" t="s">
         <v>115</v>
       </c>
@@ -3002,7 +3006,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3140,9 +3144,15 @@
       <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="53"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="36"/>
+      <c r="M32" s="53">
+        <v>46322</v>
+      </c>
+      <c r="N32" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="O32" s="36">
+        <v>5</v>
+      </c>
       <c r="Y32"/>
       <c r="AD32"/>
     </row>
@@ -3160,7 +3170,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3243,7 +3253,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3448,7 +3458,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3543,7 +3553,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3553,6 +3563,15 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3565,15 +3584,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A327D56-5B23-487D-BE83-BFF0D6C43307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEADE8E1-25DF-4FAB-924B-FE41F1C25C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -537,6 +537,10 @@
   </si>
   <si>
     <t>김창균</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤진호</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1568,6 +1572,30 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1580,21 +1608,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1611,15 +1624,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1987,52 +1991,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2072,12 +2076,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2085,7 +2089,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2097,7 +2101,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2281,7 +2285,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2328,7 +2332,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2364,7 +2368,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2374,7 +2378,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2395,10 +2399,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2412,7 +2416,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2422,7 +2426,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2441,13 +2445,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="69" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2457,7 +2461,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2467,7 +2471,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2486,10 +2490,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1150</v>
@@ -2502,7 +2506,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2512,7 +2516,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2533,13 +2537,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2551,7 +2555,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2563,7 +2567,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2589,7 +2593,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2599,7 +2603,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2626,7 +2630,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2636,7 +2640,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2667,7 +2671,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2677,7 +2681,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2703,7 +2707,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2713,7 +2717,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2739,7 +2743,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2779,7 +2783,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2818,7 +2822,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2856,7 +2860,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2894,7 +2898,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2904,7 +2908,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2916,7 +2920,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="63">
+      <c r="M26" s="57">
         <v>46235</v>
       </c>
       <c r="N26" s="34" t="s">
@@ -2932,7 +2936,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2942,7 +2946,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2952,7 +2956,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="65"/>
+      <c r="M27" s="59"/>
       <c r="N27" s="34" t="s">
         <v>115</v>
       </c>
@@ -3006,7 +3010,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3144,7 +3148,7 @@
       <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="53">
+      <c r="M32" s="57">
         <v>46322</v>
       </c>
       <c r="N32" s="37" t="s">
@@ -3170,7 +3174,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3182,9 +3186,13 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="53"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="36"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="O33" s="36">
+        <v>5</v>
+      </c>
       <c r="Y33"/>
       <c r="AD33"/>
     </row>
@@ -3253,7 +3261,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3458,7 +3466,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3553,7 +3561,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3562,16 +3570,7 @@
     </row>
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
+  <mergeCells count="22">
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3584,6 +3583,16 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M32:M33"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
